--- a/docs/requirements/DigitalSecretary-Requirements.xlsx
+++ b/docs/requirements/DigitalSecretary-Requirements.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5951,6 +5951,1089 @@
       <c r="K102" s="2" t="inlineStr">
         <is>
           <t>docs/requirements/features/email-intelligence.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>DDF-1</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Choose folder</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Pick the folder to scan</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>The user picks the root folder to scan; the choice is remembered between runs.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to pick a folder once and have it remembered.</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Browse selects a folder; it is pre-filled on the next run.</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>DDF-2</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Recursive enumeration</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Walk all subfolders</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Every file in the folder and all subfolders is visited; the checksum list file and reparse points (symlinks/junctions) are skipped.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want every file in my folder tree considered.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Subfolders are scanned; the list file and symlinks/junctions are not.</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>DDF-3</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>MD5 checksum per file</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Stream an MD5 per file</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>A streamed MD5 fingerprint is computed for every file found.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want identical files recognised by content, not name.</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Identical content yields identical MD5; large files are streamed.</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>DDF-4</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Checksum list file</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Write dedupe_md5_list.txt</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>dedupe_md5_list.txt is written in the root: MD5, size, last-modified UTC (ISO 8601) and full path, tab-separated, with a comment header.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a reusable list of checksums saved in the folder.</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>The list file exists in the root with the documented columns and header.</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>DDF-5</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Reuse existing list</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Update or use as-is</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>If the list already exists the user can update it (rescan) or use it as-is (Ask / Update / Use as-is).</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to skip a rescan when the list is already current.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Ask prompts; Update rescans; Use as-is loads the list unchanged.</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>DDF-6</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Incremental rescan</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Reuse unchanged checksums</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>A stored checksum is reused when size and last-modified time are unchanged; entries whose file is gone are pruned.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want rescans to be fast.</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Unchanged files are not rehashed; missing files leave the list.</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>DDF-7</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>In-memory index</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Load the list once</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>The list is loaded into memory once; all lookups and updates happen there.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want analysis to be fast on large folders.</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Lookups and updates use the in-memory index, not the file.</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>DDF-8</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate analysis</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Group by identical MD5</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Files are grouped by identical MD5, reporting groups, duplicate files, duplicate size and reclaimable space.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to know how much space I can reclaim.</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Groups, duplicate count, duplicate size and reclaimable space are shown.</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>DDF-9</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Show duplicates</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>List each duplicate group</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Each group is listed in the window with the copy kept and the copies that would be deleted.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to see exactly what would be deleted before it happens.</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Each group shows the kept copy and the copies to delete.</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>DDF-10</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Keeper policy</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Choose which copy to keep</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>The kept copy can be the shortest path, oldest modified, newest modified, or first alphabetically.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to control which copy survives.</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Each policy keeps the documented copy; one copy per group is always kept.</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>DDF-11</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Ignore empty files</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Skip zero-byte files</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Zero-byte files are excluded from duplicate analysis by default.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I do not want empty files treated as duplicates.</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Empty files are not grouped unless the option is turned off.</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>DDF-12</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Dry run</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Report-only by default</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Deletion is report-only by default; deleting needs Dry run turned off plus a confirmation dialog.</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want nothing deleted until I say so.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Dry run is on by default; real deletion needs it off and a confirmation.</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>DDF-13</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Byte-for-byte verification</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Verify before delete</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>A duplicate is compared byte-for-byte with the kept copy before deletion; a mismatch is skipped and logged.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want proof a file is identical before it is removed.</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Identical files are deleted; mismatches are skipped and logged.</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>DDF-14</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Recycle Bin or permanent</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Safe delete by default</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Duplicates go to the Recycle Bin by default; permanent deletion is opt-in.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to be able to undo a deletion.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Recycle Bin is the default; permanent delete needs an explicit opt-in.</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>DDF-15</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Results summary</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Show what happened</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>The results summary shows files deleted, skipped, failed, and space freed.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a clear summary of the outcome.</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Deleted, skipped, failed and space-freed figures are displayed.</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>DDF-16</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Progress, pause and resume</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Live progress and control</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Live progress is shown with Pause/Resume and Stop for both scan and delete.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to pause or stop a long job.</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Progress updates live; Pause/Resume and Stop work during scan and delete.</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>DDF-17</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Resumable work</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Autosave during scan</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>The list is autosaved periodically during a scan so a stopped scan is not redone.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I do not want to redo a long scan after stopping.</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>A stopped scan keeps its checksums and resumes from them.</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>DDF-18</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Save report</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Save a text report</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>A plain-text report of the duplicate groups and results can be saved.</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a record of what was found and done.</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Save report writes a plain-text file with groups and results.</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>DDF-19</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Settings persistence</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Remember folder and options</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>The folder and options are remembered between runs; no secrets are stored.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want my choices remembered.</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Settings round-trip; nothing secret is stored.</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
         </is>
       </c>
     </row>

--- a/docs/requirements/DigitalSecretary-Requirements.xlsx
+++ b/docs/requirements/DigitalSecretary-Requirements.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7034,6 +7034,975 @@
       <c r="K121" s="2" t="inlineStr">
         <is>
           <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>SST-1</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Choose folder</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Pick the folder to map</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>The user picks the folder to map; it is remembered; a missing folder is reported and no scan starts.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to pick a folder once and have it remembered.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Browse sets the folder; it is pre-filled next time; a missing folder shows a message.</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>SST-2</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Read-only recursive scan</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Metadata-only folder walk</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Walk all subfolders reading names, sizes and dates only; never open a file; do not follow links; log and skip unreadable folders.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a fast, safe look at any folder.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Sizes match disk; no file is opened; a junction is not counted twice; unreadable folders are logged.</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>SST-3</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Size tree with totals</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Rolled-up folder totals</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Every folder keeps total size, file/folder counts, bytes per type and newest time, consistent after a stopped scan.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want correct totals at every level.</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Totals match at every depth, including after Stop.</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>SST-4</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Size map</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Squarified treemap by type</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Draw the focused folder as a squarified treemap: area by size, colour by type, 1-3 nested levels, long tail folded into one tile.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to see at a glance what takes the space.</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Areas are proportional, tiles do not overlap, &gt;200 children fold into one tile.</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>SST-5</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Drill down</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Click to open a folder</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a folder tile (or a file's) focuses that folder; breadcrumb and Up go back; double-click a list row opens its folder.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to click into the biggest folder.</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Click changes focus; breadcrumb and Up return.</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>SST-6</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Hover details</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Tooltip per tile</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Hover shows name, size, share, count/type, date and full path.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want details without leaving the map.</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Tooltip shows the listed details.</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>SST-7</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Space by type</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart + colour legend</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart of bytes and share per file type for the focused folder; doubles as the colour key.</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to know how much is videos, photos, etc.</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Shares sum to 100%; empty types are hidden.</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>SST-8</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Space by age</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Bar chart by last change</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Bytes by time since last change: &lt;1, 1-3, 3-5, &gt;5 years.</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to see how much has sat untouched for years.</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Four buckets in age order with correct boundaries.</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>SST-9</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Largest files</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Top 100 files</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>The 100 largest files under the focused folder with size, path, type, date.</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want the biggest files listed.</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Sorted by size, ties by name, re-computed per folder.</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>SST-10</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Largest folders</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Top 100 folders</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>The 100 largest folders under the focused folder with size, path, file count.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want the biggest folders listed.</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Sorted by size; nested folders included; the folder itself excluded.</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SST-11</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Clean-up candidates</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Report-only clean-up cards</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Build/package folders, temp/partial files, installers/disk images, large (&gt;=1 GB) files unchanged 2+ years; reasons; no double counting; nothing changed.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to be pointed at space that is commonly safe to reclaim.</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Each rule matches as documented; cards sorted by size; disk unchanged.</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>SST-12</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Changes since last scan</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot + growth list</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>After a completed scan, compare with the previous gzip snapshot of the same folder and list folders changed by &gt;=1 MB.</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to see what grew lately.</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>First scan says nothing to compare; second lists grown/shrunk/new/removed folders.</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SST-13</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Progress, pause and stop</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Live progress and control</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Live counts; Pause/Resume and Stop; a stopped scan shows the partial tree and does not overwrite the snapshot.</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to control a long scan.</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Pause holds; Stop (also while paused) ends as stopped.</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>SST-14</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Explorer actions</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Show in Explorer / copy path</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Right-click a tile or row: Show in Explorer, Copy path, Open in the map.</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to act on what I found in Explorer.</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Explorer opens with the item selected; path is copied.</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>SST-15</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Save report</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Plain-text report</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Write a text report of the focused folder with every section.</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a record of the audit.</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>The file contains totals, type, age, largest, clean-up and changes.</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>SST-16</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Settings persistence</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Remember folder and map levels</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Remember the folder and map levels (clamped 1-3); nothing secret is stored.</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want my choices remembered.</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Settings round-trip; corrupt settings fall back to defaults.</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>SST-17</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Readable colours</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Colour-blind-safe palette</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>One fixed colour per type from a colour-blind-safe set; labels black/white by contrast &gt;= 3:1.</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to tell the colours apart and read the labels.</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Distinct colours; every tile colour gives its label &gt;= 3:1 contrast.</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
         </is>
       </c>
     </row>

--- a/docs/requirements/DigitalSecretary-Requirements.xlsx
+++ b/docs/requirements/DigitalSecretary-Requirements.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8003,6 +8003,1032 @@
       <c r="K138" s="2" t="inlineStr">
         <is>
           <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>SIM-1</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Choose folder &amp; settings</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Pick folder; options remembered</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>The user picks the folder; it and all options are remembered; a missing folder is reported and no scan starts.</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want my folder and choices remembered.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Folder and options are pre-filled next time.</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>SIM-2</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Find pictures</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Walk all subfolders for pictures</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Find JPEG/PNG/GIF/BMP/TIFF/HEIC/WebP/AVIF/RAW at any depth; skip links and the review folder; log unreadable folders.</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want every picture in my folder considered.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Pictures at any depth are found; other files and the review folder are not.</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>SIM-3</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Read through Windows</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Shell thumbnails + GDI+ fallback</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Read a small thumbnail via the Windows Shell (any installed codec, EXIF rotation), falling back to GDI+; read size and EXIF time incl. sub-seconds.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want HEIC and RAW included when Windows can show them.</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>JPEG/PNG read with correct size; bad files are unreadable, not crashes; fallback works.</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>SIM-4</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Visual fingerprint</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>pHash + dHash x 8 orientations</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Compute a DCT perceptual hash and a difference hash for each of 8 orientations, plus a sharpness score.</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want pictures recognised by how they look.</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Altered copies stay within the same-picture limits; turned copies match at &lt;= 2 bits.</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>SIM-5</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Fingerprint cache</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Incremental gzip cache</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Cache fingerprints per folder (gzip), reuse while size+time unchanged, autosave, prune only after a full scan.</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a second scan to be quick.</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>A rescan reads nothing unchanged; deleted files leave the cache after a full scan.</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>SIM-6</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Match kinds</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Exact / Same picture / Similar</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Classify matches as Exact (byte-verified), Same picture (tight limits, same moment) or Similar - check (looser limits).</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to know how alike two pictures are.</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Byte-identical = Exact; resized copy = Same picture; burst = Similar.</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>SIM-7</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Turned and mirrored copies</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Match 8 orientations</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Optionally match turned (90/180/270) and mirrored copies, at the same-picture limits only.</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want turned copies found too.</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Turned copies match only with the option on.</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>SIM-8</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Similar scenes and bursts</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Bursts for manual review</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Optionally group near-identical scenes and bursts, with extra tolerance within 30 s; different capture times are never Same picture.</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want bursts grouped but left for me to decide.</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Bursts are Similar, never pre-marked, and vanish with the option off.</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>SIM-9</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Strict / Balanced / Loose</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Three sensitivity levels; changing any option regroups from the cache without rescanning.</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to tune how strict matching is.</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Limits loosen from Strict to Loose; regrouping needs no rescan.</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>SIM-10</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Keeper choice</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Suggest the best picture</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Keep the most pixels, then sharpest, then biggest file, then non-copy name, then earliest, then shortest path.</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want the best picture kept.</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Each ranking step decides as documented; ties are deterministic.</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>SIM-11</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Grouping by keeper</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Star grouping, no chaining</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Each group is the best unassigned picture plus its unassigned direct matches.</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I do not want unrelated pictures pulled into a group.</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>A chain A~B~C does not put C in A's group.</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>SIM-12</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Review screen</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Groups list + side-by-side cards</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Show the groups and the selected group's pictures side by side with badges and facts.</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to compare look-alikes side by side.</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Cards show badge, name, size, dimensions, date, sharpness, match and folder.</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>SIM-13</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Toggle marks; change keeper</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Pre-mark Exact/Same; never Similar; click toggles; mark/keep all; keep another; open; Explorer; keyboard navigation.</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want the final say on every picture.</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>A click toggles a mark; Similar members start unmarked.</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>SIM-14</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Move to review folder</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Guarded, undo-able move</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Move marked pictures into the review folder keeping layout; never the keeper; skip changed files; no overwrite; confirm defaults to Cancel.</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want removed pictures kept somewhere I can check.</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Keepers never move; layout kept; clashes get (2); changed files skipped.</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>SIM-15</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Recycle Bin option</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Send to Recycle Bin instead</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Optionally send marked pictures to the Recycle Bin.</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I may prefer the Recycle Bin.</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>Recycle mode calls the recycler and leaves no undo batch.</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>SIM-16</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Undo last move</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Put the last batch back</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Restore the last moved batch, also after a restart; never overwrite.</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to undo a move.</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Undo restores every file it can and never overwrites.</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>SIM-17</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Progress, pause and stop</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Live progress and control</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Live progress; Pause/Resume and Stop; a stopped scan keeps its work and prunes nothing.</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to control a long scan.</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Pause holds; Stop ends as stopped; nothing is forgotten.</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>SIM-18</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Save report</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Plain-text report</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Write a report of every group with KEEP/MOVE and how each matches.</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a record of what was found.</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>The report lists each group, its keeper and its members.</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
         </is>
       </c>
     </row>

--- a/docs/requirements/DigitalSecretary-Requirements.xlsx
+++ b/docs/requirements/DigitalSecretary-Requirements.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K156"/>
+  <dimension ref="A1:K176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9029,6 +9029,1146 @@
       <c r="K156" s="2" t="inlineStr">
         <is>
           <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SVD-1</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Choose folder &amp; settings</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Pick folder; options remembered</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>The user picks the folder; it and all options are remembered; a missing folder is reported and no scan starts.</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want my folder and choices remembered.</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>Folder and options are pre-filled next time; corrupt settings fall back to safe defaults.</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>SVD-2</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Find videos</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Walk all subfolders for videos</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Walk every subfolder for MP4, M4V, MOV, AVI, WMV, ASF, MKV, WebM, 3GP, MTS/M2TS, TS and MPEG files; do not follow links; never scan the review folder; log and skip unreadable folders.</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want every video in my folder considered.</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>Videos at any depth are found; other files and the review folder are not.</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>SVD-3</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Skip Live Photo clips</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Leave iPhone Live Photo motion clips alone</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>By default, leave out a .MOV that has a HEIC/HEIF/JPEG still of the same name beside it (the motion part of a Live Photo); the option can be switched off.</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I do not want a clean-up to break my Live Photos.</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>A .MOV beside a same-name still is skipped with the option on and scanned with it off.</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>SVD-4</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Decode through Windows</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Media Foundation frames, upright, no padding</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Decode through Windows Media Foundation (every codec Windows has); seek to the exact time, not the nearest key frame; cut off codec padding (display aperture); apply the rotation tag; count videos that cannot be decoded; say so when Media Foundation is missing.</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want every video Windows can play included.</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>A real MP4 decodes with the right length, size and upright frames; padded frames are cropped; a non-video is unreadable, not a crash.</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>SVD-5</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Frame fingerprints</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>10 frames x (pHash + dHash) x 8 orientations</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Sample 10 frames at 5%, 15%, ... 95% of the length; fingerprint each with a perceptual hash and a difference hash in all 8 orientations; leave flat frames (black, fades, one colour) out.</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want videos recognised by what they show.</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>Flat frames carry no hash; a painted frame hashes the same through the decoder path.</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>SVD-6</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Fingerprint cache</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Incremental gzip cache</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Keep fingerprints per scanned folder, gzip-compressed in the feature's data folder; reuse them while size and modified time are unchanged; autosave during a scan; prune deleted files only after a completed scan; ignore records from another sampling plan.</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a second scan to be quick.</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>A rescan decodes nothing unchanged; deleted files leave the cache after a full scan only.</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>SVD-7</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Length gate</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Only compare videos of about the same length</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Only compare two videos whose lengths agree within 2% of the longer one or 1 second, whichever is more.</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a fast scan that never confuses a clip with a full video.</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>Lengths 2% apart match, further apart never group even with the same frames.</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>SVD-8</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Match kinds</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Exact / Same video / Similar</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Classify a match as Exact copy (same size and bytes, verified once and remembered), Same video (enough frames within the tight pHash limit and a low mean dHash) or Similar - check (looser limits, judged as-is).</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to know how alike two videos are.</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Byte-identical = Exact; a half-size low-bit-rate re-encode = Same video; another take = Similar.</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>SVD-9</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Turned and mirrored copies</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Match 8 orientations</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Optionally match a video with its 90/180/270-degree turned or mirrored version (Same video only).</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want turned copies found too.</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>Turned copies match only with the option on.</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>SVD-10</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Similar takes</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Near-identical takes for manual review</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Optionally group videos that show the same scene with differences (another take, a light edit) for manual review.</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want near-identical takes grouped but left for me to decide.</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Takes are Similar, never pre-marked, and vanish with the option off.</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>SVD-11</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Strict / Balanced / Loose</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>Strict, Balanced (default) or Loose; changing it or any matching option regroups from the cache without rescanning.</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to tune how strict matching is.</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>A stricter setting never finds more than a looser one; regrouping needs no rescan.</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>SVD-12</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Keeper choice</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Suggest the best video</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Keep the video with the most pixels, then the higher bit rate, then the longer, then the bigger file, then a name that does not look like a copy, then the earliest, then the shortest path.</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want the best version kept.</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>Each ranking step decides as documented; ties are deterministic.</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>SVD-13</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Grouping by keeper</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Star grouping, no chaining</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Each group is the best unassigned video plus its unassigned matches, so every member is compared with the keeper itself.</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I do not want unrelated videos pulled into a group.</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>A chain A~B~C does not put C in A's group; groups come most space first.</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>SVD-14</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Review screen with film strips</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Groups list + film-strip cards</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>A list of groups (match, videos, space marked) and the selected group's videos as cards: a four-frame film strip, KEEP / MOVE / keep badge, name, length, picture size, bit rate, file size, date, how it matches and its folder.</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to compare matching videos at a glance.</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Cards show the strip and all facts; the sample shows every kind of group.</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>SVD-15</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Toggle marks; change keeper; play</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Exact and Same-video members are pre-marked; Similar members never are; a click toggles a mark; Mark all / Keep all per group; Keep this one instead; Play; Show in Explorer; Previous / Next (also Ctrl+arrows, PageUp/PageDown).</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want the final say on every video.</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>A click toggles a mark; choosing another keeper pre-decides nothing.</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>SVD-16</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Move to review folder</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Guarded, undo-able move</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Move the marked videos into `_Similar videos - review` inside the scanned folder, keeping their layout; never move a keeper; skip files changed since the scan; never overwrite; confirm first, with Cancel as the default.</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want removed videos kept somewhere I can check.</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>Keepers never move; layout kept; changed files skipped.</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>SVD-17</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Recycle Bin option</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Send to Recycle Bin instead</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Alternatively send the marked videos to the Windows Recycle Bin.</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I may prefer the Recycle Bin.</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Recycle mode calls the recycler and leaves no undo batch.</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>SVD-18</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Undo last move</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Put the last batch back</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Put the last moved batch back, also after the app was closed; never overwrite a file that took a video's old place.</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to undo a move.</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Undo restores every file it can and never overwrites.</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>SVD-19</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Progress, pause and stop</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Live progress and control</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Live progress during scan and move, Pause/Resume and Stop; a stopped scan keeps the work done and prunes nothing.</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want to control a long scan.</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>Pause holds; Stop ends as stopped; autosave keeps finished work.</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>SVD-20</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Save report</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Plain-text report</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Write a report of every group with KEEP/MOVE, length, size and how each matches.</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>As a user, I want a record of what was found.</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>The report lists each group, its keeper and its members.</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
         </is>
       </c>
     </row>
